--- a/AtchisonRegime/Outputs/India/df_regZScores_India.xlsx
+++ b/AtchisonRegime/Outputs/India/df_regZScores_India.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E338"/>
+  <dimension ref="A1:E339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6011,7 +6011,7 @@
         <v>-1.609197597460336</v>
       </c>
       <c r="C328" t="n">
-        <v>0.1269752971138792</v>
+        <v>-0.1586595595287259</v>
       </c>
       <c r="D328" t="n">
         <v>0.6607631425232638</v>
@@ -6028,7 +6028,7 @@
         <v>-1.665486013574585</v>
       </c>
       <c r="C329" t="n">
-        <v>0.08629259774089702</v>
+        <v>0.1383565447898576</v>
       </c>
       <c r="D329" t="n">
         <v>0.6738196246178002</v>
@@ -6045,7 +6045,7 @@
         <v>-1.901181816225073</v>
       </c>
       <c r="C330" t="n">
-        <v>0.06631902283450167</v>
+        <v>0.1152177262296182</v>
       </c>
       <c r="D330" t="n">
         <v>0.64392862120351</v>
@@ -6062,7 +6062,7 @@
         <v>-2.093900900681109</v>
       </c>
       <c r="C331" t="n">
-        <v>0.04555869256656515</v>
+        <v>0.09314547075106079</v>
       </c>
       <c r="D331" t="n">
         <v>0.5453937035152667</v>
@@ -6079,7 +6079,7 @@
         <v>-1.925045594804248</v>
       </c>
       <c r="C332" t="n">
-        <v>0</v>
+        <v>0.0730366768494552</v>
       </c>
       <c r="D332" t="n">
         <v>0.4012988812070913</v>
@@ -6096,7 +6096,7 @@
         <v>-1.272591127701468</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.04929692066057501</v>
+        <v>0.05992091312749612</v>
       </c>
       <c r="D333" t="n">
         <v>0.2692656463854147</v>
@@ -6113,7 +6113,7 @@
         <v>-0.8244531695587767</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.05176467051398125</v>
+        <v>0.05405871173099788</v>
       </c>
       <c r="D334" t="n">
         <v>0.2201519689621168</v>
@@ -6130,7 +6130,7 @@
         <v>-0.9488965089988395</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.08209071111419658</v>
+        <v>0.05316714534512307</v>
       </c>
       <c r="D335" t="n">
         <v>0.1470370271165108</v>
@@ -6147,7 +6147,7 @@
         <v>-1.209590239554617</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.05812943059160887</v>
+        <v>0.06021053671922057</v>
       </c>
       <c r="D336" t="n">
         <v>0.1763511896644202</v>
@@ -6164,7 +6164,7 @@
         <v>-1.426764933004604</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.09280608837336365</v>
+        <v>0.07188992918729449</v>
       </c>
       <c r="D337" t="n">
         <v>0.1371594861448566</v>
@@ -6178,16 +6178,33 @@
         <v>45747</v>
       </c>
       <c r="B338" t="n">
-        <v>-1.542312882396952</v>
+        <v>-1.479076778638796</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.1977619446671215</v>
+        <v>0.08487070723497196</v>
       </c>
       <c r="D338" t="n">
         <v>0.1110546272241258</v>
       </c>
       <c r="E338" t="n">
         <v>-0.1283410707788303</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B339" t="n">
+        <v>-1.432151479563748</v>
+      </c>
+      <c r="C339" t="n">
+        <v>0.09460631327380538</v>
+      </c>
+      <c r="D339" t="n">
+        <v>-0.1433469846859853</v>
+      </c>
+      <c r="E339" t="n">
+        <v>-0.2934007498358872</v>
       </c>
     </row>
   </sheetData>
